--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1052</v>
+        <v>1399</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>881</v>
+        <v>1164</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>599</v>
+        <v>829</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,50 +1018,50 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>00215</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>SAVIGLIANO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="H15" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="J15" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="K15" s="12" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>51274</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1091,42 +1091,42 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>51274</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1145,101 +1145,101 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>00215</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SAVIGLIANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>3</v>
+        <v>129</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="G20" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="H20" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H20" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="I20" s="12" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="J21" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1415,19 +1415,19 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>12</v>
@@ -1436,26 +1436,26 @@
         <v>1</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="H24" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K24" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="L24" s="12" t="n">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,100 +1558,100 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr"/>
+          <t>ROLETTO</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F25" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="H25" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I25" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+          <t>TETTO GARETTO</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1662,12 +1662,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1677,11 +1677,11 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>0</v>
@@ -1693,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -1735,28 +1735,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>1</v>
@@ -1770,12 +1770,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1785,105 +1785,105 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1893,74 +1893,74 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>13</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J31" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J31" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="K31" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>15</v>
@@ -1969,117 +1969,117 @@
         <v>6</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+          <t>COLLEGNO</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2090,12 +2090,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2105,32 +2105,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -2144,12 +2144,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2159,51 +2159,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G36" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H36" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="J36" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2213,39 +2213,39 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2271,19 +2271,19 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>0</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2328,13 +2328,13 @@
         <v>2</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>3</v>
@@ -2382,13 +2382,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2486,13 +2486,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>93</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.3333333333333333</v>
+        <v>31</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>151</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.3642384105960265</v>
+        <v>55</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>73</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.6575342465753424</v>
+        <v>48</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>212</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.169811320754717</v>
+        <v>36</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>74</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.1891891891891892</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>188</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.02659574468085106</v>
+        <v>5</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>64</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.109375</v>
+        <v>7</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>146</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.03424657534246575</v>
+        <v>5</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>96</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.21875</v>
+        <v>21</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>77</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.3766233766233766</v>
+        <v>29</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>79</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.0379746835443038</v>
+        <v>3</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>64</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.28125</v>
+        <v>18</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>22</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.04545454545454546</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>48</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.6041666666666666</v>
+        <v>29</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>110</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.1</v>
+        <v>11</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>28</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.2142857142857143</v>
+        <v>6</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>34</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.02941176470588235</v>
+        <v>1</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>31</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.06451612903225806</v>
+        <v>2</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>46</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.1739130434782609</v>
+        <v>8</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>9</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0.1111111111111111</v>
+        <v>1</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>60</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.01666666666666667</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>33</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.09090909090909091</v>
+        <v>3</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>23</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0.391304347826087</v>
+        <v>9</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>7</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0.2857142857142857</v>
+        <v>2</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1399</v>
+        <v>1499</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1164</v>
+        <v>1245</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>829</v>
+        <v>890</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>40</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>31</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K12" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="M12" s="12" t="n">
         <v>57</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>151</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>55</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>69</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>24</v>
@@ -1004,10 +1004,10 @@
         <v>12</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,50 +1018,50 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>00215</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SAVIGLIANO</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>129</v>
       </c>
       <c r="G15" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>197</v>
+      </c>
+      <c r="M15" s="12" t="n">
         <v>5</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>14</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,50 +1072,50 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>00215</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>SAVIGLIANO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,47 +1145,47 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1199,47 +1199,47 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>133</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="I19" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="J19" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         <v>42</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>24</v>
@@ -1382,10 +1382,10 @@
         <v>4</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,50 +1396,46 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+          <t>TETTO GARETTO</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L22" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>64</v>
-      </c>
       <c r="M22" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1469,35 +1465,35 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1523,19 +1519,19 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>12</v>
@@ -1544,7 +1540,7 @@
         <v>2</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>29</v>
@@ -1558,12 +1554,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,89 +1569,93 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
+          <t>ROLETTO</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>28</v>
+        <v>114</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>6</v>
@@ -1702,14 +1702,14 @@
         <v>4</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1735,31 +1735,31 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1824,12 +1824,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1839,32 +1839,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -1878,12 +1878,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,31 +1897,31 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1932,108 +1932,108 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
         <v>16</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="M32" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M32" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>1</v>
@@ -2067,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>2</v>
@@ -2076,7 +2076,7 @@
         <v>2</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>1</v>
@@ -2090,12 +2090,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2105,23 +2105,23 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="G35" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="H35" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>3</v>
@@ -2130,26 +2130,26 @@
         <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2159,35 +2159,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2198,12 +2198,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2213,39 +2213,39 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G37" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H37" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="J37" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
@@ -2328,13 +2328,13 @@
         <v>2</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>3</v>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
@@ -2486,13 +2486,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -1404,7 +1404,11 @@
           <t>TETTO GARETTO</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>SCIALO' MARCO</t>
@@ -2048,7 +2052,11 @@
           <t>COLLEGNO</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>GUERRA GIUSEPPE</t>
@@ -2206,11 +2214,7 @@
           <t>TORINO</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
@@ -2422,7 +2426,11 @@
           <t>GASSINO TORINESE</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Emanuele</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
@@ -2526,11 +2534,7 @@
           <t>IVREA</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
           <t>DELLI CARRI LUCA</t>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -2372,11 +2372,7 @@
           <t>ORBASSANO</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>PODESTÀ ANDREA</t>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1499</v>
+        <v>1604</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1245</v>
+        <v>1337</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>890</v>
+        <v>947</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>40</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>31</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>141</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>38</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>24</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>27</v>
@@ -1058,10 +1058,10 @@
         <v>8</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>14</v>
@@ -1112,7 +1112,7 @@
         <v>33</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>14</v>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>9</v>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>11</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>24</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G20" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I20" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="H20" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>47</v>
-      </c>
       <c r="J20" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>32</v>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>18</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6</v>
@@ -1396,120 +1396,120 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="G22" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="M22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1523,47 +1523,47 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1577,35 +1577,35 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1634,13 +1634,13 @@
         <v>32</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>28</v>
@@ -1652,7 +1652,7 @@
         <v>7</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>11</v>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>0</v>
@@ -1703,10 +1703,10 @@
         <v>6</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -1739,22 +1739,22 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>5</v>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>4</v>
@@ -1814,7 +1814,7 @@
         <v>9</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>2</v>
@@ -1847,22 +1847,22 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>0</v>
@@ -1922,14 +1922,14 @@
         <v>2</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1955,19 +1955,19 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>9</v>
@@ -1976,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>16</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>1</v>
@@ -2075,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>2</v>
@@ -2117,19 +2117,19 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G35" s="12" t="n">
         <v>13</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>10</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>3</v>
@@ -2138,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2221,19 +2221,19 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>0</v>
@@ -2242,7 +2242,7 @@
         <v>2</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>3</v>
@@ -2281,7 +2281,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>2</v>
@@ -2332,13 +2332,13 @@
         <v>2</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>3</v>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1604</v>
+        <v>1700</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1337</v>
+        <v>1418</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>947</v>
+        <v>1002</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>12</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>50</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>27</v>
@@ -1058,7 +1058,7 @@
         <v>8</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>6</v>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1148,13 +1148,13 @@
         <v>77</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>60</v>
@@ -1166,26 +1166,26 @@
         <v>14</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="K18" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="M18" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>24</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         <v>38</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>1</v>
@@ -1490,10 +1490,10 @@
         <v>15</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1523,47 +1523,47 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="M24" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1580,32 +1580,32 @@
         <v>34</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,31 +1685,31 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1742,13 +1742,13 @@
         <v>30</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>24</v>
@@ -1760,7 +1760,7 @@
         <v>5</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>2</v>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>35</v>
-      </c>
       <c r="M29" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,39 +1843,39 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1922,14 +1922,14 @@
         <v>2</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
@@ -1976,64 +1976,64 @@
         <v>0</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
         <v>16</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>1</v>
@@ -2075,16 +2075,16 @@
         <v>1</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>1</v>
@@ -2098,50 +2098,50 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="M35" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2171,19 +2171,19 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>3</v>
@@ -2192,60 +2192,64 @@
         <v>0</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
+          <t>ALPIGNANO</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="J37" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2256,66 +2260,62 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+          <t>TORINO</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2325,39 +2325,39 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F39" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="G39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>173</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1700</v>
+        <v>1832</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1418</v>
+        <v>1540</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1002</v>
+        <v>1075</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="G11" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>212</v>
+      </c>
+      <c r="J11" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="H11" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>199</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>79</v>
-      </c>
       <c r="K11" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,35 +983,35 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>27</v>
@@ -1058,10 +1058,10 @@
         <v>8</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>34</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>34</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,35 +1145,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>8</v>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1415,35 +1415,35 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>3</v>
@@ -1481,7 +1481,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>3</v>
@@ -1490,7 +1490,7 @@
         <v>15</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>9</v>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1523,47 +1523,47 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1577,47 +1577,47 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="M25" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F25" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
         <v>34</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J27" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K27" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L27" s="12" t="n">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>2</v>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M31" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="H34" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,50 +2098,50 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
         <v>16</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,54 +2152,54 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>184</v>
+        <v>5</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
         <v>11</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>9</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2382,13 +2382,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -2268,7 +2268,11 @@
           <t>TORINO</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -866,7 +866,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2268,11 +2268,7 @@
           <t>TORINO</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
@@ -2480,11 +2476,7 @@
           <t>ALBA</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
           <t>GIARRATANA SEARA</t>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -2422,11 +2422,7 @@
           <t>GASSINO TORINESE</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Emanuele</t>
-        </is>
-      </c>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N43" headerRowCount="1">
-  <autoFilter ref="A10:N43"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O43" headerRowCount="1">
+  <autoFilter ref="A10:O43"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>SS 28 SUD KM. 25 FRAZ.SANTUARIO</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>265</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>219</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>92</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>92</v>
       </c>
       <c r="I11" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="J11" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIA TORINO 135</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>SCIALO' MARCO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>242</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>196</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>SS20 KM12+230</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>C.SO PRIMO LEVI - S.P.N.7 KM.8+260 160/A</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>VIA TORINO 116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>155</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>239</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIA LIGURIA 1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>SS 11 KM 25+300</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>STRADA PROV.53 KM 12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>DELLI CARRI LUCA</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>SS 10 KM 18+000</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>SS 26 KM 1</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>DELLI CARRI LUCA</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H22" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K22" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>SCIALO' MARCO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>LARGO TIRRENO 0123</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>CORSO ROMA SS 10 0017</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F26" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="H26" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>S.S. 589 KM. 27+770</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>SCIALO' MARCO</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="M28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>SP.CHIVASSO-OZEGNA KM22</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>VIA ALTESSANO 158</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K31" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="M33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>CSO UNIONE SOVIETICA 614/A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>STRADA TRAFORO DEL MONTE BIANCO SNC</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>DELLI CARRI LUCA</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K35" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>C.SO BARALE</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>SCIALO' MARCO</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>S.S. 24 KM.16+760 S.N.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="M37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2268,40 +2419,45 @@
           <t>TORINO</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>C.SO CASALE 292A</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2320,42 +2476,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>VIA PIERA CILLARIO</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>Nadir Abdel</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="M39" s="12" t="n">
+      <c r="N39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2372,27 +2533,29 @@
           <t>ORBASSANO</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>CIRCONV TO/PIOSSASCO</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>PODESTÀ ANDREA</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
       </c>
@@ -2405,7 +2568,10 @@
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2422,27 +2588,29 @@
           <t>GASSINO TORINESE</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>STRADA CHIVASSO, 24</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>BRESCIA FEDERICO</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J41" s="12" t="n">
         <v>0</v>
       </c>
@@ -2455,7 +2623,10 @@
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2472,27 +2643,29 @@
           <t>ALBA</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>C.SO M. COPPINO N° 54</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>GIARRATANA SEARA</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="G42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" s="12" t="n">
         <v>0</v>
       </c>
@@ -2505,7 +2678,10 @@
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="N42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2522,27 +2698,29 @@
           <t>IVREA</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>VIA JERVIS 84</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>DELLI CARRI LUCA</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="G43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" s="12" t="n">
         <v>0</v>
       </c>
@@ -2555,7 +2733,10 @@
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="N43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1832</v>
+        <v>1906</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1540</v>
+        <v>1600</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1075</v>
+        <v>1159</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L12" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>212</v>
+      </c>
+      <c r="N12" s="12" t="n">
         <v>71</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>196</v>
-      </c>
-      <c r="N12" s="12" t="n">
-        <v>67</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,52 +1019,52 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>00215</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>SAVIGLIANO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA TORINO 116</t>
+          <t>VIA LIGURIA 1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,35 +1074,35 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>239</v>
+        <v>109</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>00215</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SAVIGLIANO</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA LIGURIA 1</t>
+          <t>VIA TORINO 116</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,35 +1133,35 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>106</v>
+        <v>252</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>00591</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROV.53 KM 12</t>
+          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,35 +1251,35 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>100</v>
+        <v>197</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>00591</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA BOTTICELLI 62/A - VIA BOTTICELLI ADIACENTE 60 62/A</t>
+          <t>STRADA PROV.53 KM 12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,39 +1310,39 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1432,16 +1432,16 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>53</v>
@@ -1450,17 +1450,17 @@
         <v>7</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>25</v>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
+          <t>S.S. 589 KM. 27+770</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1553,49 +1553,49 @@
         <v>39</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>LARGO TIRRENO 0123</t>
+          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CORSO ROMA SS 10 0017</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1668,52 +1668,52 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G25" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>80</v>
-      </c>
       <c r="H25" s="12" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA S.FRANCESCO DI SALES NO 14</t>
+          <t>CORSO ROMA SS 10 0017</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>22</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>S.S. 589 KM. 27+770</t>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
+          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
         <v>31</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>40</v>
-      </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>31</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>26</v>
@@ -1984,7 +1984,7 @@
         <v>11</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>2</v>
@@ -2025,13 +2025,13 @@
         <v>25</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>26</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>2</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
+          <t>CSO UNIONE SOVIETICA 614/A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,35 +2077,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="I32" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K33" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="N33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M33" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CSO UNIONE SOVIETICA 614/A</t>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,19 +2258,19 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>3</v>
@@ -2279,10 +2279,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>16</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2434,13 +2434,13 @@
         <v>10</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>9</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0</v>
@@ -2511,14 +2511,14 @@
         <v>0</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1906</v>
+        <v>2005</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1600</v>
+        <v>1680</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1159</v>
+        <v>1216</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>71</v>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1022,13 +1022,13 @@
         <v>129</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>119</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>112</v>
@@ -1040,10 +1040,10 @@
         <v>17</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>37</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>16</v>
@@ -1099,10 +1099,10 @@
         <v>35</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,16 +1137,16 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>84</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>83</v>
@@ -1155,10 +1155,10 @@
         <v>27</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>8</v>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>13</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>27</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>29</v>
@@ -1335,7 +1335,7 @@
         <v>9</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>8</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 18+000</t>
+          <t>SS 26 KM 1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SS 26 KM 1</t>
+          <t>SS 10 KM 18+000</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="H21" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="G21" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>69</v>
-      </c>
       <c r="I21" s="12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1491,22 +1491,22 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>0</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>13</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
+          <t>CORSO ROMA SS 10 0017</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="H24" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L24" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="M24" s="12" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>LARGO TIRRENO 0123</t>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CORSO ROMA SS 10 0017</t>
+          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA S.FRANCESCO DI SALES NO 14</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
         <v>38</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H27" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="N27" s="12" t="n">
         <v>25</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="N27" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
+          <t>SP.CHIVASSO-OZEGNA KM22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SP.CHIVASSO-OZEGNA KM22</t>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,39 +1959,39 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
         <v>31</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K30" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J30" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L30" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>CSO UNIONE SOVIETICA 614/A</t>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="K32" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
+          <t>CSO UNIONE SOVIETICA 614/A</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,35 +2136,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G33" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H33" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="I33" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K34" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="N34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M34" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>STRADA TRAFORO DEL MONTE BIANCO SNC</t>
+          <t>S.S. 24 KM.16+760 S.N.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K35" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>C.SO BARALE</t>
+          <t>STRADA TRAFORO DEL MONTE BIANCO SNC</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,35 +2313,35 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J36" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="N36" s="12" t="n">
         <v>15</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N36" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>S.S. 24 KM.16+760 S.N.</t>
+          <t>C.SO BARALE</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,39 +2372,39 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K37" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L37" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M37" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2434,13 +2434,13 @@
         <v>10</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>9</v>
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>2</v>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2005</v>
+        <v>2143</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1680</v>
+        <v>1792</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1216</v>
+        <v>1322</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
+        <v>304</v>
+      </c>
+      <c r="G11" s="12" t="n">
         <v>291</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>257</v>
-      </c>
       <c r="H11" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>49</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>54</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>13</v>
@@ -1255,52 +1255,52 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROV.53 KM 12</t>
+          <t>SS 10 KM 18+000</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="I19" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="K19" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J19" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="L19" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SS 26 KM 1</t>
+          <t>STRADA PROV.53 KM 12</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K20" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="N20" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="N20" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 18+000</t>
+          <t>SS 26 KM 1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>0</v>
@@ -1512,31 +1512,31 @@
         <v>0</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>S.S. 589 KM. 27+770</t>
+          <t>VIA ALTESSANO 158</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>63</v>
+        <v>214</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>153</v>
+        <v>17</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA S.FRANCESCO DI SALES NO 14</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
+          <t>S.S. 589 KM. 27+770</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L26" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>162</v>
+      </c>
+      <c r="N26" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="M26" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="N26" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>LARGO TIRRENO 0123</t>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
+          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>SP.CHIVASSO-OZEGNA KM22</t>
+          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K29" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L29" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L29" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="M29" s="12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
+          <t>SP.CHIVASSO-OZEGNA KM22</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA ALTESSANO 158</t>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,39 +2018,39 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2081,35 +2081,35 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="K32" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2140,19 +2140,19 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>12</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>5</v>
@@ -2220,14 +2220,14 @@
         <v>3</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2258,35 +2258,35 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>3</v>
@@ -2338,10 +2338,10 @@
         <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>16</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
@@ -2434,13 +2434,13 @@
         <v>10</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>9</v>
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2143</v>
+        <v>2256</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1792</v>
+        <v>1873</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1322</v>
+        <v>1419</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I12" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>207</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>241</v>
+      </c>
+      <c r="N12" s="12" t="n">
         <v>82</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>201</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>234</v>
-      </c>
-      <c r="N12" s="12" t="n">
-        <v>80</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>38</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>38</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>13</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>51</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1376,13 +1376,13 @@
         <v>79</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>64</v>
@@ -1394,7 +1394,7 @@
         <v>9</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>8</v>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>28</v>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
+          <t>VIA ALTESSANO 158</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,56 +1487,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA ALTESSANO 158</t>
+          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,39 +1546,39 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="H23" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>214</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="N23" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>41</v>
@@ -1668,35 +1668,35 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="H25" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="I25" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00259</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>TETTO GARETTO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA S.FRANCESCO DI SALES NO 14</t>
+          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>00259</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>TETTO GARETTO</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA SAVONA 82 - LOC. TETTO GARETTO</t>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1904,52 +1904,52 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SP.CHIVASSO-OZEGNA KM22</t>
+          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,35 +1959,35 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K30" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L30" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L30" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="M30" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>8</v>
@@ -2050,24 +2050,24 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
+          <t>SP.CHIVASSO-OZEGNA KM22</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,39 +2077,39 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2140,31 +2140,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
+          <t>S.S. 24 KM.16+760 S.N.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="K34" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>S.S. 24 KM.16+760 S.N.</t>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J35" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="K35" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>3</v>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>3</v>
@@ -2338,10 +2338,10 @@
         <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2411,95 +2411,95 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>C.SO CASALE 292A</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>VIA PIERA CILLARIO</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
         <v>10</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H38" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M38" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA PIERA CILLARIO</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+          <t>C.SO CASALE 292A</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>9</v>
@@ -2508,17 +2508,17 @@
         <v>0</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2256</v>
+        <v>2366</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1873</v>
+        <v>1966</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1419</v>
+        <v>1495</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>51</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>56</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>38</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>13</v>
@@ -1255,35 +1255,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>51</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>29</v>
@@ -1394,7 +1394,7 @@
         <v>9</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>8</v>
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>28</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>3</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>5</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CORSO ROMA SS 10 0017</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>LARGO TIRRENO 0123</t>
+          <t>CORSO ROMA SS 10 0017</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>12</v>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>10</v>
@@ -1866,10 +1866,10 @@
         <v>7</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
+          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1904,52 +1904,52 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K29" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L29" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L29" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="M29" s="12" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00779</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>OZEGNA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
+          <t>SP.CHIVASSO-OZEGNA KM22</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SP.CHIVASSO-OZEGNA KM22</t>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,39 +2077,39 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>36</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>24</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2140,52 +2140,52 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>S.S. 24 KM.16+760 S.N.</t>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H34" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I34" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J34" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
+          <t>S.S. 24 KM.16+760 S.N.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2258,35 +2258,35 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>42</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>3</v>
@@ -2379,7 +2379,7 @@
         <v>16</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
@@ -2456,14 +2456,14 @@
         <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2493,13 +2493,13 @@
         <v>10</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>9</v>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>33</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2366</v>
+        <v>2500</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1966</v>
+        <v>2082</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1495</v>
+        <v>1620</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>40</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L15" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>151</v>
+      </c>
+      <c r="N15" s="12" t="n">
         <v>38</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>144</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>34</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1199,13 +1199,13 @@
         <v>102</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>81</v>
@@ -1217,7 +1217,7 @@
         <v>18</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>13</v>
@@ -1258,13 +1258,13 @@
         <v>97</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>85</v>
@@ -1276,10 +1276,10 @@
         <v>12</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>51</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>40</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>00544</t>
+          <t>00521</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CALUSO</t>
+          <t>CHIVASSO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROV.53 KM 12</t>
+          <t>SS 26 KM 1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>00521</t>
+          <t>00544</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CHIVASSO</t>
+          <t>CALUSO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SS 26 KM 1</t>
+          <t>STRADA PROV.53 KM 12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K21" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>132</v>
+      </c>
+      <c r="N21" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L21" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>147</v>
-      </c>
-      <c r="N21" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>3</v>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>LARGO TIRRENO 0123</t>
+          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00687</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MONCALIERI</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CORSO ROMA SS 10 0017</t>
+          <t>S.S. 589 KM. 27+770</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="I25" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>188</v>
+      </c>
+      <c r="N25" s="12" t="n">
         <v>32</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="N25" s="12" t="n">
-        <v>41</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>00687</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>MONCALIERI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>S.S. 589 KM. 27+770</t>
+          <t>CORSO ROMA SS 10 0017</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>1</v>
@@ -1804,34 +1804,34 @@
         <v>4</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>00728</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CARMAGNOLA</t>
+          <t>POIRINO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA S.FRANCESCO DI SALES NO 14</t>
+          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>00836</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CHIERI</t>
+          <t>CARMAGNOLA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
+          <t>VIA S.FRANCESCO DI SALES NO 14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M29" s="12" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>00728</t>
+          <t>00836</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>POIRINO</t>
+          <t>CHIERI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>S.S.29  BIVIO DI PESSIONE S.N.</t>
+          <t>S.S. 10 AL KM 14+400 - CORSO TORINO 45</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K30" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L30" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L30" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="M30" s="12" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,16 +2022,16 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>26</v>
@@ -2040,10 +2040,10 @@
         <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>3</v>
@@ -2102,7 +2102,7 @@
         <v>2</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
@@ -2140,19 +2140,19 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>14</v>
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G34" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="H34" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>8</v>
@@ -2220,14 +2220,14 @@
         <v>3</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>11</v>
@@ -2279,14 +2279,14 @@
         <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2323,10 +2323,10 @@
         <v>42</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>22</v>
@@ -2338,10 +2338,10 @@
         <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>16</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2493,13 +2493,13 @@
         <v>10</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>9</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O43" headerRowCount="1">
-  <autoFilter ref="A10:O43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O44" headerRowCount="1">
+  <autoFilter ref="A10:O44"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2500</v>
+        <v>2623</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2082</v>
+        <v>2198</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1620</v>
+        <v>1748</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>44</v>
@@ -1040,10 +1040,10 @@
         <v>25</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>00215</t>
+          <t>00635</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SAVIGLIANO</t>
+          <t>SETTIMO TORINESE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA LIGURIA 1</t>
+          <t>VIA TORINO 116</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,35 +1074,35 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>40</v>
+        <v>151</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>151</v>
+        <v>356</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>00635</t>
+          <t>00215</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SETTIMO TORINESE</t>
+          <t>SAVIGLIANO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA TORINO 116</t>
+          <t>VIA LIGURIA 1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,35 +1133,35 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>332</v>
+        <v>161</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>13</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1255,35 +1255,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>29</v>
@@ -1335,10 +1335,10 @@
         <v>18</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>28</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>00501</t>
+          <t>00991</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>ROLETTO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>LARGO TIRRENO 0123</t>
+          <t>S.S. 589 KM. 27+770</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>111</v>
+        <v>199</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>00501</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SAINT-CHRISTOPHE</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
+          <t>LARGO TIRRENO 0123</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>00991</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ROLETTO</t>
+          <t>SAINT-CHRISTOPHE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>S.S. 589 KM. 27+770</t>
+          <t>S.S. N. 26 KM 99+263 - LOC. GRAND CHEMIN  SNC</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,39 +1664,39 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>56</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>52</v>
@@ -1748,10 +1748,10 @@
         <v>5</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
@@ -1863,17 +1863,17 @@
         <v>8</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>37</v>
@@ -1922,17 +1922,17 @@
         <v>10</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>14</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1966,13 +1966,13 @@
         <v>42</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>35</v>
@@ -1984,14 +1984,14 @@
         <v>6</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>37</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>36</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>6</v>
@@ -2102,14 +2102,14 @@
         <v>2</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2140,19 +2140,19 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>14</v>
@@ -2161,14 +2161,14 @@
         <v>0</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <v>30</v>
-      </c>
-      <c r="G34" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>29</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>8</v>
@@ -2220,14 +2220,14 @@
         <v>3</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2258,35 +2258,35 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>42</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>20</v>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>C.SO BARALE</t>
+          <t>VIA PIERA CILLARIO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
         <v>16</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="N37" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M37" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA PIERA CILLARIO</t>
+          <t>C.SO BARALE</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,39 +2431,39 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2493,13 +2493,13 @@
         <v>10</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>9</v>
@@ -2739,6 +2739,61 @@
       <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>00918</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>S.S. 23 AL KM.20+500 S.N.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>SCIALO' MARCO</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -684,13 +684,13 @@
         <v>34</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2623</v>
+        <v>2588</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2198</v>
+        <v>2183</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1748</v>
+        <v>1709</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>00779</t>
+          <t>00284</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>OZEGNA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SP.CHIVASSO-OZEGNA KM22</t>
+          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>00284</t>
+          <t>00585</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA CUNEO ANG. VIA ROSSELLI 136</t>
+          <t>CSO UNIONE SOVIETICA 614/A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>PODESTÀ ANDREA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>0</v>
@@ -2096,16 +2096,16 @@
         <v>37</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>00585</t>
+          <t>00978</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CSO UNIONE SOVIETICA 614/A</t>
+          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,35 +2136,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>PODESTÀ ANDREA</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>00978</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>ALPIGNANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>C.SO SACCO E VANZETTI  (DIR. SUD)  9</t>
+          <t>S.S. 24 KM.16+760 S.N.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>116</v>
+        <v>15</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>00015</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ALPIGNANO</t>
+          <t>COURMAYEUR</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>S.S. 24 KM.16+760 S.N.</t>
+          <t>STRADA TRAFORO DEL MONTE BIANCO SNC</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>DELLI CARRI LUCA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>00015</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>COURMAYEUR</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>STRADA TRAFORO DEL MONTE BIANCO SNC</t>
+          <t>VIA PIERA CILLARIO</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>DELLI CARRI LUCA</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA PIERA CILLARIO</t>
+          <t>C.SO BARALE</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,94 +2372,90 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
         <v>16</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>C.SO BARALE</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+          <t>C.SO CASALE 292A</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>35</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,51 +2466,51 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>00607</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>C.SO CASALE 292A</t>
+          <t>CORSO FRANCIA 6</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MERONI GIULIA LUIGIA.xlsx
@@ -684,13 +684,13 @@
         <v>34</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2588</v>
+        <v>2592</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2183</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1709</v>
+        <v>1682</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>116</v>
@@ -863,14 +863,14 @@
         <v>55</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>63</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>86</v>
@@ -922,7 +922,7 @@
         <v>98</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>124</v>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>125</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>115</v>
@@ -981,7 +981,7 @@
         <v>17</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>58</v>
@@ -1022,16 +1022,16 @@
         <v>158</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>94</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>44</v>
@@ -1040,10 +1040,10 @@
         <v>25</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>151</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>35</v>
@@ -1099,7 +1099,7 @@
         <v>14</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>14</v>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>22</v>
@@ -1158,7 +1158,7 @@
         <v>39</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>45</v>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>28</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>33</v>
@@ -1217,14 +1217,14 @@
         <v>18</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>13</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1258,16 +1258,16 @@
         <v>106</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>28</v>
@@ -1276,10 +1276,10 @@
         <v>12</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>87</v>
@@ -1326,7 +1326,7 @@
         <v>56</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>29</v>
@@ -1335,7 +1335,7 @@
         <v>18</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>41</v>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>62</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>13</v>
@@ -1394,14 +1394,14 @@
         <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>28</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>43</v>
@@ -1444,7 +1444,7 @@
         <v>31</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>36</v>
@@ -1453,14 +1453,14 @@
         <v>9</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>11</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>44</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>34</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>124</v>
@@ -1562,7 +1562,7 @@
         <v>101</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>23</v>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>87</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>27</v>
@@ -1630,7 +1630,7 @@
         <v>2</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>27</v>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>31</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>34</v>
@@ -1739,7 +1739,7 @@
         <v>47</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>21</v>
@@ -1798,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>5</v>
@@ -1848,7 +1848,7 @@
         <v>46</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>36</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>8</v>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>10</v>
@@ -1925,14 +1925,14 @@
         <v>8</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>14</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>57</v>
@@ -1975,7 +1975,7 @@
         <v>57</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>14</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>6</v>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>14</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>22</v>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>13</v>
@@ -2152,7 +2152,7 @@
         <v>14</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>8</v>
@@ -2161,14 +2161,14 @@
         <v>3</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>12</v>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2264,13 +2264,13 @@
         <v>42</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>4</v>
@@ -2279,31 +2279,31 @@
         <v>0</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>00350</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>BORGO SAN DALMAZZO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA PIERA CILLARIO</t>
+          <t>C.SO BARALE</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>GIARRATANA SEARA</t>
+          <t>SCIALO' MARCO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>00350</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>BORGO SAN DALMAZZO</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>C.SO BARALE</t>
+          <t>VIA PIERA CILLARIO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,90 +2372,90 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>SCIALO' MARCO</t>
+          <t>GIARRATANA SEARA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
         <v>16</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="N37" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M37" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>51318</t>
+          <t>00607</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>TORINO</t>
+          <t>COLLEGNO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>C.SO CASALE 292A</t>
+          <t>CORSO FRANCIA 6</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA FEDERICO</t>
+          <t>GUERRA GIUSEPPE</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2466,51 +2466,51 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>00607</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>COLLEGNO</t>
+          <t>TORINO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>CORSO FRANCIA 6</t>
+          <t>C.SO CASALE 292A</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>GUERRA GIUSEPPE</t>
+          <t>BRESCIA FEDERICO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2544,13 +2544,13 @@
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
@@ -2599,13 +2599,13 @@
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2654,13 +2654,13 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>0</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
